--- a/src/evaluation/data/processed/RES_deprivation_aware_model_travel_time_from_sample_to_hospital.xlsx
+++ b/src/evaluation/data/processed/RES_deprivation_aware_model_travel_time_from_sample_to_hospital.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>49.257259</v>
+        <v>49.25726</v>
       </c>
       <c r="F2" t="n">
         <v>6.852541</v>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.276946</v>
+        <v>49.27695</v>
       </c>
       <c r="F3" t="n">
         <v>6.870121</v>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49.237085</v>
+        <v>49.23709</v>
       </c>
       <c r="F4" t="n">
         <v>6.99259</v>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49.153009</v>
+        <v>49.15301</v>
       </c>
       <c r="F5" t="n">
         <v>7.048336</v>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.297734</v>
+        <v>49.29773</v>
       </c>
       <c r="F6" t="n">
         <v>7.054714</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.495769</v>
+        <v>49.49577</v>
       </c>
       <c r="F7" t="n">
         <v>6.596771</v>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49.495769</v>
+        <v>49.49577</v>
       </c>
       <c r="F8" t="n">
         <v>6.596771</v>
@@ -698,13 +698,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49.457186</v>
+        <v>49.45719</v>
       </c>
       <c r="F9" t="n">
         <v>6.631578</v>
       </c>
       <c r="G9" t="n">
-        <v>11.96</v>
+        <v>11.97</v>
       </c>
       <c r="H9" t="n">
         <v>11.2</v>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49.457186</v>
+        <v>49.45719</v>
       </c>
       <c r="F10" t="n">
         <v>6.631578</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49.537868</v>
+        <v>49.53787</v>
       </c>
       <c r="F11" t="n">
         <v>6.88934</v>
@@ -788,16 +788,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>49.3838646832488</v>
+        <v>49.41257</v>
       </c>
       <c r="F12" t="n">
-        <v>6.970938009703829</v>
+        <v>6.909871</v>
       </c>
       <c r="G12" t="n">
-        <v>9.98</v>
+        <v>18.12</v>
       </c>
       <c r="H12" t="n">
-        <v>4.17</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="13">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49.35300457549134</v>
+        <v>49.45443</v>
       </c>
       <c r="F13" t="n">
-        <v>7.067610052120797</v>
+        <v>7.093187</v>
       </c>
       <c r="G13" t="n">
-        <v>9.42</v>
+        <v>19.82</v>
       </c>
       <c r="H13" t="n">
-        <v>5.45</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="14">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>49.38758241991242</v>
+        <v>49.45443</v>
       </c>
       <c r="F14" t="n">
-        <v>7.127547669466786</v>
+        <v>7.093187</v>
       </c>
       <c r="G14" t="n">
-        <v>10.71</v>
+        <v>17.27</v>
       </c>
       <c r="H14" t="n">
-        <v>5.54</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -878,16 +878,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49.38758241991242</v>
+        <v>49.34829</v>
       </c>
       <c r="F15" t="n">
-        <v>7.127547669466786</v>
+        <v>7.185803</v>
       </c>
       <c r="G15" t="n">
-        <v>8.31</v>
+        <v>13.85</v>
       </c>
       <c r="H15" t="n">
-        <v>4.84</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="16">
@@ -908,16 +908,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>49.454659</v>
+        <v>49.39309</v>
       </c>
       <c r="F16" t="n">
-        <v>7.186793</v>
+        <v>7.242613</v>
       </c>
       <c r="G16" t="n">
-        <v>10.01</v>
+        <v>8.24</v>
       </c>
       <c r="H16" t="n">
-        <v>8.57</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="17">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>49.266127</v>
+        <v>49.26613</v>
       </c>
       <c r="F17" t="n">
         <v>6.68297</v>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49.328624</v>
+        <v>49.32862</v>
       </c>
       <c r="F18" t="n">
         <v>6.714977</v>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49.315236</v>
+        <v>49.31524</v>
       </c>
       <c r="F19" t="n">
         <v>6.756487</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49.419092</v>
+        <v>49.41909</v>
       </c>
       <c r="F20" t="n">
         <v>6.88979</v>
@@ -1058,16 +1058,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49.45243115437203</v>
+        <v>49.41909</v>
       </c>
       <c r="F21" t="n">
-        <v>6.936411212283481</v>
+        <v>6.88979</v>
       </c>
       <c r="G21" t="n">
-        <v>7.65</v>
+        <v>11.06</v>
       </c>
       <c r="H21" t="n">
-        <v>5.21</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="22">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>49.153009</v>
+        <v>49.15301</v>
       </c>
       <c r="F22" t="n">
         <v>7.048336</v>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49.290552</v>
+        <v>49.22916</v>
       </c>
       <c r="F23" t="n">
-        <v>7.113175</v>
+        <v>7.263907</v>
       </c>
       <c r="G23" t="n">
-        <v>26.42</v>
+        <v>21.21</v>
       </c>
       <c r="H23" t="n">
-        <v>13.56</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="24">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>49.317756</v>
+        <v>49.22916</v>
       </c>
       <c r="F24" t="n">
-        <v>7.227015</v>
+        <v>7.263907</v>
       </c>
       <c r="G24" t="n">
-        <v>20.75</v>
+        <v>18.54</v>
       </c>
       <c r="H24" t="n">
-        <v>11.5</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="25">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49.317756</v>
+        <v>49.31776</v>
       </c>
       <c r="F25" t="n">
         <v>7.227015</v>
@@ -1208,16 +1208,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>49.308199</v>
+        <v>49.3736</v>
       </c>
       <c r="F26" t="n">
-        <v>7.351777</v>
+        <v>7.312062</v>
       </c>
       <c r="G26" t="n">
-        <v>19.25</v>
+        <v>15.37</v>
       </c>
       <c r="H26" t="n">
-        <v>8.199999999999999</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="27">
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49.51343375036538</v>
+        <v>49.55541</v>
       </c>
       <c r="F27" t="n">
-        <v>6.987445810416845</v>
+        <v>7.015395</v>
       </c>
       <c r="G27" t="n">
-        <v>9.949999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="H27" t="n">
-        <v>6.4</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="28">
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49.52935016254072</v>
+        <v>49.51569</v>
       </c>
       <c r="F28" t="n">
-        <v>7.002075168874315</v>
+        <v>7.073571</v>
       </c>
       <c r="G28" t="n">
-        <v>8.390000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="H28" t="n">
-        <v>4.22</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="29">
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>49.52935016254072</v>
+        <v>49.51569</v>
       </c>
       <c r="F29" t="n">
-        <v>7.002075168874315</v>
+        <v>7.073571</v>
       </c>
       <c r="G29" t="n">
-        <v>12.69</v>
+        <v>7.13</v>
       </c>
       <c r="H29" t="n">
-        <v>11.25</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="30">
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>49.454659</v>
+        <v>49.56146</v>
       </c>
       <c r="F30" t="n">
-        <v>7.186793</v>
+        <v>7.12658</v>
       </c>
       <c r="G30" t="n">
-        <v>15.19</v>
+        <v>10.84</v>
       </c>
       <c r="H30" t="n">
-        <v>11.82</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="31">
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>49.454659</v>
+        <v>49.56146</v>
       </c>
       <c r="F31" t="n">
-        <v>7.186793</v>
+        <v>7.12658</v>
       </c>
       <c r="G31" t="n">
-        <v>24.64</v>
+        <v>16.62</v>
       </c>
       <c r="H31" t="n">
-        <v>18.77</v>
+        <v>11.94</v>
       </c>
     </row>
   </sheetData>
